--- a/Convention_Reference.xlsx
+++ b/Convention_Reference.xlsx
@@ -1151,7 +1151,8 @@
       <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Business days after the accrual period ends before the coupon is paid.
-0 = pay on the last day of the period</t>
+T+N is counted from the ADJUSTED period end (Bloomberg/ISDA standard).
+0 = pay on the last day of the adjusted period</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1567,8 @@
       <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Business days after the compounding period ends before the floating coupon is settled.
-Payment date = unadjusted period end + delay, then rolled by floating_pay_date_adj</t>
+T+N is counted from the ADJUSTED period end (Bloomberg/ISDA standard), then rolled by floating_pay_date_adj.
+Example: period ends Sunday May 10 -&gt; adjusts to Monday May 11 -&gt; T+2 = Wednesday May 13</t>
         </is>
       </c>
     </row>
